--- a/data/internalStats2/File1/RPT_RPT5713512752455CZ_internalStats2.xlsx
+++ b/data/internalStats2/File1/RPT_RPT5713512752455CZ_internalStats2.xlsx
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>40639.24873580507</v>
+        <v>40639.24873580508</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>380.9455392214938</v>
@@ -2221,10 +2221,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="164" t="n">
-        <v>50.13676844737647</v>
+        <v>50.13676844737645</v>
       </c>
       <c r="T10" s="161" t="n">
-        <v>41070.33104347394</v>
+        <v>41070.33104347395</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" thickBot="1">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="P12" s="165" t="n">
-        <v>88833.896862031</v>
+        <v>88833.89686203102</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>5138.937154405056</v>
@@ -2660,13 +2660,13 @@
         </is>
       </c>
       <c r="P26" s="185" t="n">
-        <v>5520.587381943595</v>
+        <v>5520.587381943594</v>
       </c>
       <c r="Q26" s="186" t="n">
-        <v>0.05847875100647596</v>
+        <v>0.05847875100647595</v>
       </c>
       <c r="R26" s="185" t="n">
-        <v>605.745548086862</v>
+        <v>605.7455480868618</v>
       </c>
       <c r="S26" s="187" t="n">
         <v>7909.979579883866</v>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="P28" s="185" t="n">
-        <v>5138.937154405056</v>
+        <v>5138.937154405055</v>
       </c>
       <c r="Q28" s="186" t="n">
-        <v>0.05443598760401831</v>
+        <v>0.05443598760401828</v>
       </c>
       <c r="R28" s="185" t="n">
         <v>7.014014537180778</v>
@@ -2828,10 +2828,10 @@
         <v>927236.1362523314</v>
       </c>
       <c r="T28" s="84" t="n">
-        <v>732.6670235945372</v>
+        <v>732.667023594537</v>
       </c>
       <c r="U28" s="188" t="n">
-        <v>0.6101035440899032</v>
+        <v>0.6101035440899031</v>
       </c>
       <c r="W28" s="184" t="n">
         <v>4</v>
@@ -3712,16 +3712,16 @@
         </is>
       </c>
       <c r="P40" s="185" t="n">
-        <v>1562.181632578948</v>
+        <v>1562.181632578949</v>
       </c>
       <c r="Q40" s="186" t="n">
-        <v>0.01654795484575989</v>
+        <v>0.0165479548457599</v>
       </c>
       <c r="R40" s="185" t="n">
         <v>208.6456182454549</v>
       </c>
       <c r="S40" s="187" t="n">
-        <v>5964.419580898265</v>
+        <v>5964.419580898266</v>
       </c>
       <c r="T40" s="84" t="n">
         <v>7.487248693337843</v>
@@ -4032,16 +4032,16 @@
         </is>
       </c>
       <c r="P44" s="206" t="n">
-        <v>774.5378194108405</v>
+        <v>774.5378194108404</v>
       </c>
       <c r="Q44" s="207" t="n">
-        <v>0.008204562513505409</v>
+        <v>0.008204562513505407</v>
       </c>
       <c r="R44" s="206" t="n">
         <v>171.8704802224944</v>
       </c>
       <c r="S44" s="208" t="n">
-        <v>6398.884314999521</v>
+        <v>6398.884314999522</v>
       </c>
       <c r="T44" s="120" t="n">
         <v>4.506520365848544</v>
@@ -6294,7 +6294,7 @@
         <v>0.0336090367932811</v>
       </c>
       <c r="AB78" s="190" t="n">
-        <v>9267.033172801768</v>
+        <v>9267.033172801766</v>
       </c>
     </row>
     <row r="79">
@@ -6491,10 +6491,10 @@
         <v>18.74202829953412</v>
       </c>
       <c r="S81" s="187" t="n">
-        <v>90778.30001633604</v>
+        <v>90778.30001633606</v>
       </c>
       <c r="T81" s="84" t="n">
-        <v>26.84406721519591</v>
+        <v>26.8440672151959</v>
       </c>
       <c r="U81" s="197" t="n">
         <v>0.1779539760038236</v>
@@ -7341,10 +7341,10 @@
         <v>26170.09160450426</v>
       </c>
       <c r="Q97" s="177" t="n">
-        <v>0.6372018666419462</v>
+        <v>0.637201866641946</v>
       </c>
       <c r="R97" s="176" t="n">
-        <v>1528.42481492836</v>
+        <v>1528.424814928359</v>
       </c>
       <c r="S97" s="178" t="n">
         <v>51536.05404104013</v>
@@ -7416,7 +7416,7 @@
         <v>3184.536013900853</v>
       </c>
       <c r="Q98" s="186" t="n">
-        <v>0.07753860105315305</v>
+        <v>0.07753860105315304</v>
       </c>
       <c r="R98" s="185" t="n">
         <v>962.3076730454776</v>
@@ -7641,7 +7641,7 @@
         <v>1797.222431534498</v>
       </c>
       <c r="Q101" s="186" t="n">
-        <v>0.04375962856574239</v>
+        <v>0.04375962856574236</v>
       </c>
       <c r="R101" s="185" t="n">
         <v>285.2517725340086</v>
@@ -8092,19 +8092,19 @@
         <v>380.9455392214938</v>
       </c>
       <c r="Q107" s="186" t="n">
-        <v>0.009275443599864189</v>
+        <v>0.009275443599864186</v>
       </c>
       <c r="R107" s="185" t="n">
         <v>13.29491345016598</v>
       </c>
       <c r="S107" s="187" t="n">
-        <v>68735.32304496143</v>
+        <v>68735.32304496145</v>
       </c>
       <c r="T107" s="84" t="n">
-        <v>28.65348019371559</v>
+        <v>28.65348019371558</v>
       </c>
       <c r="U107" s="197" t="n">
-        <v>0.2117360409405025</v>
+        <v>0.2117360409405024</v>
       </c>
       <c r="W107" s="184" t="n">
         <v>11</v>
@@ -8167,7 +8167,7 @@
         <v>331.3032322739321</v>
       </c>
       <c r="Q108" s="186" t="n">
-        <v>0.008066729043971902</v>
+        <v>0.008066729043971901</v>
       </c>
       <c r="R108" s="185" t="n">
         <v>300.3410617405242</v>
@@ -8242,7 +8242,7 @@
         <v>201.0636192451115</v>
       </c>
       <c r="Q109" s="186" t="n">
-        <v>0.004895592855881312</v>
+        <v>0.004895592855881311</v>
       </c>
       <c r="R109" s="185" t="n">
         <v>207.0262154212766</v>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="O145" s="237" t="n">
-        <v>42512.23371758816</v>
+        <v>42512.23371758815</v>
       </c>
       <c r="P145" s="72" t="n">
         <v>41.3512867871618</v>
@@ -9102,7 +9102,7 @@
         <v>15991.84448858188</v>
       </c>
       <c r="P146" s="84" t="n">
-        <v>34.17181086340696</v>
+        <v>34.17181086340697</v>
       </c>
       <c r="Q146" s="84" t="n">
         <v>34.06389988173305</v>
@@ -9123,7 +9123,7 @@
         </is>
       </c>
       <c r="O147" s="239" t="n">
-        <v>7439.915137529334</v>
+        <v>7439.915137529335</v>
       </c>
       <c r="P147" s="84" t="n">
         <v>13.63594514274421</v>
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="O299" s="237" t="n">
-        <v>42512.23371758816</v>
+        <v>42512.23371758815</v>
       </c>
       <c r="P299" s="72" t="n">
         <v>41.3512867871618</v>
@@ -11428,7 +11428,7 @@
         <v>15991.84448858188</v>
       </c>
       <c r="P300" s="84" t="n">
-        <v>34.17181086340696</v>
+        <v>34.17181086340697</v>
       </c>
       <c r="Q300" s="84" t="n">
         <v>34.06389988173305</v>
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="O301" s="239" t="n">
-        <v>7439.915137529334</v>
+        <v>7439.915137529335</v>
       </c>
       <c r="P301" s="84" t="n">
         <v>13.63594514274421</v>
@@ -15493,7 +15493,7 @@
         <v>0.0008747898504468416</v>
       </c>
       <c r="AO634" s="190" t="n">
-        <v>1759.174773375929</v>
+        <v>1759.174773375928</v>
       </c>
     </row>
     <row r="635">
@@ -16449,7 +16449,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="160" t="n">
-        <v>67.36121965193101</v>
+        <v>67.36121965193099</v>
       </c>
       <c r="T8" s="161" t="n">
         <v>23975.91740725807</v>
@@ -16484,7 +16484,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>44541.71688923958</v>
+        <v>44541.71688923957</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>0</v>
@@ -16493,10 +16493,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="164" t="n">
-        <v>63.67344266100181</v>
+        <v>63.67344266100179</v>
       </c>
       <c r="T10" s="161" t="n">
-        <v>44605.39033190058</v>
+        <v>44605.39033190057</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" thickBot="1">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="P12" s="165" t="n">
-        <v>90226.12145387538</v>
+        <v>90226.12145387537</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>0</v>
@@ -16537,10 +16537,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="167" t="n">
-        <v>265.508634699221</v>
+        <v>265.5086346992209</v>
       </c>
       <c r="T12" s="168" t="n">
-        <v>90491.6300885746</v>
+        <v>90491.63008857459</v>
       </c>
     </row>
     <row r="13"/>
@@ -16854,10 +16854,10 @@
         </is>
       </c>
       <c r="P25" s="176" t="n">
-        <v>51479.2874751646</v>
+        <v>51479.28747516461</v>
       </c>
       <c r="Q25" s="177" t="n">
-        <v>0.568884519206648</v>
+        <v>0.5688845192066482</v>
       </c>
       <c r="R25" s="176" t="n">
         <v>1200.527210337816</v>
@@ -16869,7 +16869,7 @@
         <v>42.88056699746012</v>
       </c>
       <c r="U25" s="179" t="n">
-        <v>0.01881328097315777</v>
+        <v>0.01881328097315778</v>
       </c>
       <c r="W25" s="175" t="n">
         <v>1</v>
@@ -16888,7 +16888,7 @@
         <v>1867.819787149833</v>
       </c>
       <c r="AA25" s="180" t="n">
-        <v>0.8194811991398094</v>
+        <v>0.8194811991398097</v>
       </c>
       <c r="AB25" s="181" t="n">
         <v>2332562.454599021</v>
@@ -16966,7 +16966,7 @@
         <v>2.155992992460939</v>
       </c>
       <c r="AA26" s="189" t="n">
-        <v>0.0009459133771652175</v>
+        <v>0.0009459133771652178</v>
       </c>
       <c r="AB26" s="190" t="n">
         <v>112773.4381232263</v>
@@ -17013,7 +17013,7 @@
         <v>5758.614189381809</v>
       </c>
       <c r="Q27" s="186" t="n">
-        <v>0.06363698149480995</v>
+        <v>0.06363698149480997</v>
       </c>
       <c r="R27" s="185" t="n">
         <v>629.9102787609263</v>
@@ -17025,7 +17025,7 @@
         <v>9.141959392549317</v>
       </c>
       <c r="U27" s="188" t="n">
-        <v>0.004010913631515561</v>
+        <v>0.004010913631515562</v>
       </c>
       <c r="W27" s="184" t="n">
         <v>3</v>
@@ -17091,7 +17091,7 @@
         <v>4648.157765468977</v>
       </c>
       <c r="Q28" s="186" t="n">
-        <v>0.05136560984611824</v>
+        <v>0.05136560984611825</v>
       </c>
       <c r="R28" s="185" t="n">
         <v>1007.0360290917</v>
@@ -17122,7 +17122,7 @@
         <v>63.51854929769291</v>
       </c>
       <c r="AA28" s="189" t="n">
-        <v>0.0278679224324541</v>
+        <v>0.02786792243245411</v>
       </c>
       <c r="AB28" s="190" t="n">
         <v>67560.70387513375</v>
@@ -17169,7 +17169,7 @@
         <v>3835.88036112893</v>
       </c>
       <c r="Q29" s="186" t="n">
-        <v>0.04238933874187381</v>
+        <v>0.04238933874187382</v>
       </c>
       <c r="R29" s="185" t="n">
         <v>589.052645033237</v>
@@ -17247,7 +17247,7 @@
         <v>3140.191975803396</v>
       </c>
       <c r="Q30" s="186" t="n">
-        <v>0.03470146324836592</v>
+        <v>0.03470146324836593</v>
       </c>
       <c r="R30" s="185" t="n">
         <v>490.4806047028345</v>
@@ -17259,7 +17259,7 @@
         <v>6.402275534841854</v>
       </c>
       <c r="U30" s="197" t="n">
-        <v>0.002808913616083669</v>
+        <v>0.00280891361608367</v>
       </c>
       <c r="W30" s="184" t="n">
         <v>6</v>
@@ -17311,7 +17311,7 @@
         <v>2847.999563655173</v>
       </c>
       <c r="Q31" s="186" t="n">
-        <v>0.03147251918069668</v>
+        <v>0.03147251918069669</v>
       </c>
       <c r="R31" s="185" t="n">
         <v>352.5867747611161</v>
@@ -17323,7 +17323,7 @@
         <v>8.077442965876257</v>
       </c>
       <c r="U31" s="197" t="n">
-        <v>0.003543871144956826</v>
+        <v>0.003543871144956827</v>
       </c>
       <c r="W31" s="184" t="n">
         <v>7</v>
@@ -17342,7 +17342,7 @@
         <v>8.077442965876257</v>
       </c>
       <c r="AA31" s="189" t="n">
-        <v>0.003543871144956826</v>
+        <v>0.003543871144956827</v>
       </c>
       <c r="AB31" s="190" t="n">
         <v>17386.06995079163</v>
@@ -17383,7 +17383,7 @@
         <v>2715.676752360251</v>
       </c>
       <c r="Q32" s="186" t="n">
-        <v>0.03001025343119695</v>
+        <v>0.03001025343119696</v>
       </c>
       <c r="R32" s="185" t="n">
         <v>400.0767942280105</v>
@@ -17395,7 +17395,7 @@
         <v>6.787888704218473</v>
       </c>
       <c r="U32" s="197" t="n">
-        <v>0.002978096288105285</v>
+        <v>0.002978096288105287</v>
       </c>
       <c r="W32" s="184" t="n">
         <v>8</v>
@@ -17414,7 +17414,7 @@
         <v>6.942429228798463</v>
       </c>
       <c r="AA32" s="189" t="n">
-        <v>0.003045898896938203</v>
+        <v>0.003045898896938204</v>
       </c>
       <c r="AB32" s="190" t="n">
         <v>17044.66297125357</v>
@@ -17464,7 +17464,7 @@
         <v>0.02560945994805869</v>
       </c>
       <c r="R33" s="185" t="n">
-        <v>476.4131410179262</v>
+        <v>476.4131410179261</v>
       </c>
       <c r="S33" s="187" t="n">
         <v>3497.290207285741</v>
@@ -17473,7 +17473,7 @@
         <v>4.864353177656564</v>
       </c>
       <c r="U33" s="197" t="n">
-        <v>0.00213417054605053</v>
+        <v>0.002134170546050531</v>
       </c>
       <c r="W33" s="184" t="n">
         <v>9</v>
@@ -17707,7 +17707,7 @@
         <v>5.413110708547088</v>
       </c>
       <c r="U36" s="197" t="n">
-        <v>0.002374930646433326</v>
+        <v>0.002374930646433327</v>
       </c>
       <c r="W36" s="184" t="n">
         <v>12</v>
@@ -17726,7 +17726,7 @@
         <v>9.026955487378377</v>
       </c>
       <c r="AA36" s="189" t="n">
-        <v>0.003960457190929795</v>
+        <v>0.003960457190929796</v>
       </c>
       <c r="AB36" s="190" t="n">
         <v>8934.79617000783</v>
@@ -17773,7 +17773,7 @@
         <v>825.4853483728185</v>
       </c>
       <c r="Q37" s="186" t="n">
-        <v>0.009122228736125327</v>
+        <v>0.009122228736125329</v>
       </c>
       <c r="R37" s="185" t="n">
         <v>414.6972528919617</v>
@@ -17785,7 +17785,7 @@
         <v>1.99057346682708</v>
       </c>
       <c r="U37" s="197" t="n">
-        <v>0.0008733377506726713</v>
+        <v>0.0008733377506726716</v>
       </c>
       <c r="W37" s="184" t="n">
         <v>13</v>
@@ -17804,7 +17804,7 @@
         <v>13.39308931175454</v>
       </c>
       <c r="AA37" s="189" t="n">
-        <v>0.00587604059282982</v>
+        <v>0.005876040592829821</v>
       </c>
       <c r="AB37" s="190" t="n">
         <v>8505.25352201269</v>
@@ -17863,7 +17863,7 @@
         <v>2.227141504817263</v>
       </c>
       <c r="U38" s="197" t="n">
-        <v>0.0009771288448585669</v>
+        <v>0.0009771288448585671</v>
       </c>
       <c r="W38" s="184" t="n">
         <v>14</v>
@@ -17882,7 +17882,7 @@
         <v>4.961994115947533</v>
       </c>
       <c r="AA38" s="189" t="n">
-        <v>0.002177009214826984</v>
+        <v>0.002177009214826985</v>
       </c>
       <c r="AB38" s="190" t="n">
         <v>8243.779468153201</v>
@@ -17915,7 +17915,7 @@
         <v>540.1023682568547</v>
       </c>
       <c r="Q39" s="186" t="n">
-        <v>0.005968533970801434</v>
+        <v>0.005968533970801435</v>
       </c>
       <c r="R39" s="185" t="n">
         <v>311.5156994066005</v>
@@ -17927,7 +17927,7 @@
         <v>1.733788599693961</v>
       </c>
       <c r="U39" s="197" t="n">
-        <v>0.0007606767903986036</v>
+        <v>0.0007606767903986038</v>
       </c>
       <c r="W39" s="184" t="n">
         <v>15</v>
@@ -17946,7 +17946,7 @@
         <v>4.775784957707994</v>
       </c>
       <c r="AA39" s="189" t="n">
-        <v>0.002095312412311683</v>
+        <v>0.002095312412311684</v>
       </c>
       <c r="AB39" s="190" t="n">
         <v>6781.217652820743</v>
@@ -17987,7 +17987,7 @@
         <v>483.691127765949</v>
       </c>
       <c r="Q40" s="186" t="n">
-        <v>0.005345147692582227</v>
+        <v>0.005345147692582228</v>
       </c>
       <c r="R40" s="185" t="n">
         <v>139.4896493872805</v>
@@ -17999,7 +17999,7 @@
         <v>3.467577199387922</v>
       </c>
       <c r="U40" s="197" t="n">
-        <v>0.001521353580797207</v>
+        <v>0.001521353580797208</v>
       </c>
       <c r="W40" s="184" t="n">
         <v>16</v>
@@ -18018,7 +18018,7 @@
         <v>6.797705117969311</v>
       </c>
       <c r="AA40" s="189" t="n">
-        <v>0.002982403109655808</v>
+        <v>0.002982403109655809</v>
       </c>
       <c r="AB40" s="190" t="n">
         <v>5771.404397198206</v>
@@ -18067,7 +18067,7 @@
         <v>357.0902727289035</v>
       </c>
       <c r="Q41" s="186" t="n">
-        <v>0.003946113827095147</v>
+        <v>0.003946113827095148</v>
       </c>
       <c r="R41" s="185" t="n">
         <v>309.4583173984886</v>
@@ -18079,7 +18079,7 @@
         <v>1.153920423696608</v>
       </c>
       <c r="U41" s="197" t="n">
-        <v>0.0005062673064224036</v>
+        <v>0.0005062673064224038</v>
       </c>
       <c r="W41" s="184" t="n">
         <v>17</v>
@@ -18098,7 +18098,7 @@
         <v>0.9357509383225104</v>
       </c>
       <c r="AA41" s="189" t="n">
-        <v>0.0004105483335749773</v>
+        <v>0.0004105483335749774</v>
       </c>
       <c r="AB41" s="190" t="n">
         <v>5515.725846949021</v>
@@ -18159,7 +18159,7 @@
         <v>1.153920423696608</v>
       </c>
       <c r="U42" s="197" t="n">
-        <v>0.0005062673064224036</v>
+        <v>0.0005062673064224038</v>
       </c>
       <c r="W42" s="184" t="n">
         <v>18</v>
@@ -18227,7 +18227,7 @@
         <v>164.3013003104025</v>
       </c>
       <c r="Q43" s="186" t="n">
-        <v>0.001815651902276286</v>
+        <v>0.001815651902276287</v>
       </c>
       <c r="R43" s="185" t="n">
         <v>125.2186189598836</v>
@@ -18239,7 +18239,7 @@
         <v>1.312115575743891</v>
       </c>
       <c r="U43" s="197" t="n">
-        <v>0.0005756733346643629</v>
+        <v>0.000575673334664363</v>
       </c>
       <c r="W43" s="184" t="n">
         <v>19</v>
@@ -18307,7 +18307,7 @@
         <v>80.28978246687787</v>
       </c>
       <c r="Q44" s="207" t="n">
-        <v>0.0008872619753704181</v>
+        <v>0.0008872619753704183</v>
       </c>
       <c r="R44" s="206" t="n">
         <v>18.52354606116344</v>
@@ -18319,7 +18319,7 @@
         <v>4.334471499234902</v>
       </c>
       <c r="U44" s="209" t="n">
-        <v>0.001901691975996509</v>
+        <v>0.00190169197599651</v>
       </c>
       <c r="W44" s="205" t="n">
         <v>20</v>
@@ -19382,7 +19382,7 @@
         <v>3.058286585773696</v>
       </c>
       <c r="AA60" s="189" t="n">
-        <v>0.001592353533099476</v>
+        <v>0.001592353533099477</v>
       </c>
       <c r="AB60" s="190" t="n">
         <v>1950.563553730203</v>
@@ -21329,7 +21329,7 @@
         <v>33401.23966684753</v>
       </c>
       <c r="Q97" s="177" t="n">
-        <v>0.7488162174641897</v>
+        <v>0.7488162174641899</v>
       </c>
       <c r="R97" s="176" t="n">
         <v>1551.914559664297</v>
@@ -21357,10 +21357,10 @@
         </is>
       </c>
       <c r="Z97" s="72" t="n">
-        <v>73.04755851294583</v>
+        <v>73.04755851294581</v>
       </c>
       <c r="AA97" s="180" t="n">
-        <v>0.4159681964456066</v>
+        <v>0.4159681964456064</v>
       </c>
       <c r="AB97" s="181" t="n">
         <v>172911.1146243992</v>
@@ -21404,7 +21404,7 @@
         <v>3486.118324101733</v>
       </c>
       <c r="Q98" s="186" t="n">
-        <v>0.0781546422565112</v>
+        <v>0.07815464225651121</v>
       </c>
       <c r="R98" s="185" t="n">
         <v>1007.0360290917</v>
@@ -21479,7 +21479,7 @@
         <v>2876.910270846698</v>
       </c>
       <c r="Q99" s="186" t="n">
-        <v>0.06449691953013151</v>
+        <v>0.06449691953013152</v>
       </c>
       <c r="R99" s="185" t="n">
         <v>883.5789675498555</v>
@@ -21855,7 +21855,7 @@
         <v>483.691127765949</v>
       </c>
       <c r="Q104" s="186" t="n">
-        <v>0.01084378197717566</v>
+        <v>0.01084378197717567</v>
       </c>
       <c r="R104" s="185" t="n">
         <v>139.4896493872805</v>
@@ -21930,7 +21930,7 @@
         <v>357.0902727289035</v>
       </c>
       <c r="Q105" s="186" t="n">
-        <v>0.008005540811813547</v>
+        <v>0.008005540811813549</v>
       </c>
       <c r="R105" s="185" t="n">
         <v>309.4583173984886</v>
@@ -23485,7 +23485,7 @@
         <v>0</v>
       </c>
       <c r="P164" s="84" t="n">
-        <v>65.65184583143797</v>
+        <v>65.65184583143798</v>
       </c>
       <c r="Q164" s="84" t="n">
         <v>0</v>
@@ -25709,7 +25709,7 @@
         <v>0</v>
       </c>
       <c r="P315" s="84" t="n">
-        <v>65.65184583143797</v>
+        <v>65.65184583143798</v>
       </c>
       <c r="Q315" s="84" t="n">
         <v>0</v>
@@ -28806,7 +28806,7 @@
         <v>1867.819787149833</v>
       </c>
       <c r="AN607" s="180" t="n">
-        <v>0.8194811991398094</v>
+        <v>0.8194811991398097</v>
       </c>
       <c r="AO607" s="181" t="n">
         <v>2332562.454599021</v>
@@ -28830,7 +28830,7 @@
         <v>2.155992992460939</v>
       </c>
       <c r="AN608" s="189" t="n">
-        <v>0.0009459133771652175</v>
+        <v>0.0009459133771652178</v>
       </c>
       <c r="AO608" s="190" t="n">
         <v>112773.4381232263</v>
@@ -28878,7 +28878,7 @@
         <v>63.51854929769291</v>
       </c>
       <c r="AN610" s="189" t="n">
-        <v>0.0278679224324541</v>
+        <v>0.02786792243245411</v>
       </c>
       <c r="AO610" s="190" t="n">
         <v>67560.70387513375</v>
@@ -28950,7 +28950,7 @@
         <v>8.077442965876257</v>
       </c>
       <c r="AN613" s="189" t="n">
-        <v>0.003543871144956826</v>
+        <v>0.003543871144956827</v>
       </c>
       <c r="AO613" s="190" t="n">
         <v>17386.06995079163</v>
@@ -28974,7 +28974,7 @@
         <v>6.942429228798463</v>
       </c>
       <c r="AN614" s="189" t="n">
-        <v>0.003045898896938203</v>
+        <v>0.003045898896938204</v>
       </c>
       <c r="AO614" s="190" t="n">
         <v>17044.66297125357</v>
@@ -29070,7 +29070,7 @@
         <v>9.026955487378377</v>
       </c>
       <c r="AN618" s="189" t="n">
-        <v>0.003960457190929795</v>
+        <v>0.003960457190929796</v>
       </c>
       <c r="AO618" s="190" t="n">
         <v>8934.79617000783</v>
@@ -29094,7 +29094,7 @@
         <v>13.39308931175454</v>
       </c>
       <c r="AN619" s="189" t="n">
-        <v>0.00587604059282982</v>
+        <v>0.005876040592829821</v>
       </c>
       <c r="AO619" s="190" t="n">
         <v>8505.25352201269</v>
@@ -29118,7 +29118,7 @@
         <v>4.961994115947533</v>
       </c>
       <c r="AN620" s="189" t="n">
-        <v>0.002177009214826984</v>
+        <v>0.002177009214826985</v>
       </c>
       <c r="AO620" s="190" t="n">
         <v>8243.779468153201</v>
@@ -29142,7 +29142,7 @@
         <v>4.775784957707994</v>
       </c>
       <c r="AN621" s="189" t="n">
-        <v>0.002095312412311683</v>
+        <v>0.002095312412311684</v>
       </c>
       <c r="AO621" s="190" t="n">
         <v>6781.217652820743</v>
@@ -29166,7 +29166,7 @@
         <v>6.797705117969311</v>
       </c>
       <c r="AN622" s="189" t="n">
-        <v>0.002982403109655808</v>
+        <v>0.002982403109655809</v>
       </c>
       <c r="AO622" s="190" t="n">
         <v>5771.404397198206</v>
@@ -29190,7 +29190,7 @@
         <v>0.9357509383225104</v>
       </c>
       <c r="AN623" s="189" t="n">
-        <v>0.0004105483335749773</v>
+        <v>0.0004105483335749774</v>
       </c>
       <c r="AO623" s="190" t="n">
         <v>5515.725846949021</v>
@@ -29310,7 +29310,7 @@
         <v>1.99057346682708</v>
       </c>
       <c r="AN628" s="189" t="n">
-        <v>0.0008733377506726713</v>
+        <v>0.0008733377506726716</v>
       </c>
       <c r="AO628" s="190" t="n">
         <v>4202.675151630569</v>
@@ -29334,7 +29334,7 @@
         <v>5.790177970411065</v>
       </c>
       <c r="AN629" s="189" t="n">
-        <v>0.002540363914693199</v>
+        <v>0.0025403639146932</v>
       </c>
       <c r="AO629" s="190" t="n">
         <v>4093.706320536365</v>
@@ -29382,7 +29382,7 @@
         <v>1.236461488363929</v>
       </c>
       <c r="AN631" s="189" t="n">
-        <v>0.0005424811055893286</v>
+        <v>0.0005424811055893287</v>
       </c>
       <c r="AO631" s="190" t="n">
         <v>3978.236598878418</v>
@@ -29406,7 +29406,7 @@
         <v>2.98586020024062</v>
       </c>
       <c r="AN632" s="189" t="n">
-        <v>0.001310006626009007</v>
+        <v>0.001310006626009008</v>
       </c>
       <c r="AO632" s="190" t="n">
         <v>3955.541358315622</v>
@@ -29454,7 +29454,7 @@
         <v>5.675356150003923</v>
       </c>
       <c r="AN634" s="189" t="n">
-        <v>0.0024899873613865</v>
+        <v>0.002489987361386501</v>
       </c>
       <c r="AO634" s="190" t="n">
         <v>3819.693206660515</v>
@@ -29478,7 +29478,7 @@
         <v>2.133296533745063</v>
       </c>
       <c r="AN635" s="189" t="n">
-        <v>0.000935955606435583</v>
+        <v>0.0009359556064355831</v>
       </c>
       <c r="AO635" s="190" t="n">
         <v>3608.75503451883</v>
@@ -29526,7 +29526,7 @@
         <v>3.095577774140608</v>
       </c>
       <c r="AN637" s="189" t="n">
-        <v>0.001358143758747852</v>
+        <v>0.001358143758747853</v>
       </c>
       <c r="AO637" s="190" t="n">
         <v>1994.166817997918</v>
@@ -29574,7 +29574,7 @@
         <v>0.9952867334135399</v>
       </c>
       <c r="AN639" s="189" t="n">
-        <v>0.0004366688753363357</v>
+        <v>0.0004366688753363358</v>
       </c>
       <c r="AO639" s="190" t="n">
         <v>1978.479852686568</v>
@@ -29622,7 +29622,7 @@
         <v>10.9692656257673</v>
       </c>
       <c r="AN641" s="189" t="n">
-        <v>0.004812620045322279</v>
+        <v>0.00481262004532228</v>
       </c>
       <c r="AO641" s="190" t="n">
         <v>1647.759564238029</v>
@@ -29670,7 +29670,7 @@
         <v>0.941852359014839</v>
       </c>
       <c r="AN643" s="189" t="n">
-        <v>0.0004132252511126352</v>
+        <v>0.0004132252511126353</v>
       </c>
       <c r="AO643" s="190" t="n">
         <v>1582.52717314179</v>
@@ -29694,7 +29694,7 @@
         <v>5.689511084835286</v>
       </c>
       <c r="AN644" s="189" t="n">
-        <v>0.002496197651613188</v>
+        <v>0.002496197651613189</v>
       </c>
       <c r="AO644" s="190" t="n">
         <v>1128.685209009624</v>
@@ -29718,7 +29718,7 @@
         <v>1.33591344695991</v>
       </c>
       <c r="AN645" s="189" t="n">
-        <v>0.0005861143355442375</v>
+        <v>0.0005861143355442376</v>
       </c>
       <c r="AO645" s="190" t="n">
         <v>1120.160331729499</v>
@@ -29790,7 +29790,7 @@
         <v>0.7987194484834893</v>
       </c>
       <c r="AN648" s="189" t="n">
-        <v>0.0003504275818912456</v>
+        <v>0.0003504275818912457</v>
       </c>
       <c r="AO648" s="190" t="n">
         <v>830.2904449631906</v>
@@ -29814,7 +29814,7 @@
         <v>1.99057346682708</v>
       </c>
       <c r="AN649" s="189" t="n">
-        <v>0.0008733377506726713</v>
+        <v>0.0008733377506726716</v>
       </c>
       <c r="AO649" s="190" t="n">
         <v>676.8065511957866</v>
@@ -29838,7 +29838,7 @@
         <v>1.185378011352536</v>
       </c>
       <c r="AN650" s="189" t="n">
-        <v>0.0005200689064652334</v>
+        <v>0.0005200689064652335</v>
       </c>
       <c r="AO650" s="190" t="n">
         <v>674.3035107796646</v>
@@ -29862,7 +29862,7 @@
         <v>0.7873952985415297</v>
       </c>
       <c r="AN651" s="189" t="n">
-        <v>0.0003454592610513445</v>
+        <v>0.0003454592610513446</v>
       </c>
       <c r="AO651" s="190" t="n">
         <v>664.917586097855</v>
@@ -29934,7 +29934,7 @@
         <v>0.9952867334135399</v>
       </c>
       <c r="AN654" s="189" t="n">
-        <v>0.0004366688753363357</v>
+        <v>0.0004366688753363358</v>
       </c>
       <c r="AO654" s="190" t="n">
         <v>535.75849421705</v>
@@ -29982,7 +29982,7 @@
         <v>0.1797265991720041</v>
       </c>
       <c r="AN656" s="189" t="n">
-        <v>7.885266556231157e-05</v>
+        <v>7.885266556231159e-05</v>
       </c>
       <c r="AO656" s="190" t="n">
         <v>402.1661877448232</v>
@@ -30006,7 +30006,7 @@
         <v>0.169124309614495</v>
       </c>
       <c r="AN657" s="189" t="n">
-        <v>7.420105140767578e-05</v>
+        <v>7.420105140767579e-05</v>
       </c>
       <c r="AO657" s="190" t="n">
         <v>327.5155885603752</v>
@@ -30030,7 +30030,7 @@
         <v>0.9952867334135399</v>
       </c>
       <c r="AN658" s="189" t="n">
-        <v>0.0004366688753363357</v>
+        <v>0.0004366688753363358</v>
       </c>
       <c r="AO658" s="190" t="n">
         <v>256.1513655263169</v>
@@ -30054,7 +30054,7 @@
         <v>0.1377616586356387</v>
       </c>
       <c r="AN659" s="189" t="n">
-        <v>6.044110357482053e-05</v>
+        <v>6.044110357482055e-05</v>
       </c>
       <c r="AO659" s="190" t="n">
         <v>135.8295374124733</v>
@@ -30078,7 +30078,7 @@
         <v>1.99057346682708</v>
       </c>
       <c r="AN660" s="189" t="n">
-        <v>0.0008733377506726713</v>
+        <v>0.0008733377506726716</v>
       </c>
       <c r="AO660" s="190" t="n">
         <v>103.2657417095713</v>
@@ -30102,7 +30102,7 @@
         <v>0.9952867334135399</v>
       </c>
       <c r="AN661" s="189" t="n">
-        <v>0.0004366688753363357</v>
+        <v>0.0004366688753363358</v>
       </c>
       <c r="AO661" s="190" t="n">
         <v>101.7205141909832</v>
@@ -30126,7 +30126,7 @@
         <v>0.1128835197094509</v>
       </c>
       <c r="AN662" s="189" t="n">
-        <v>4.952614954132214e-05</v>
+        <v>4.952614954132216e-05</v>
       </c>
       <c r="AO662" s="190" t="n">
         <v>73.46207826511703</v>
@@ -30150,7 +30150,7 @@
         <v>1.312115575743891</v>
       </c>
       <c r="AN663" s="189" t="n">
-        <v>0.0005756733346643629</v>
+        <v>0.000575673334664363</v>
       </c>
       <c r="AO663" s="190" t="n">
         <v>37.2646071973568</v>
@@ -30174,7 +30174,7 @@
         <v>0.02031495125115925</v>
       </c>
       <c r="AN664" s="189" t="n">
-        <v>8.912915863885376e-06</v>
+        <v>8.912915863885378e-06</v>
       </c>
       <c r="AO664" s="190" t="n">
         <v>14.30886932257346</v>
@@ -30578,7 +30578,7 @@
         <v>30.90605424508733</v>
       </c>
       <c r="T8" s="161" t="n">
-        <v>25313.63572990606</v>
+        <v>25313.63572990607</v>
       </c>
     </row>
     <row r="9">
@@ -30597,7 +30597,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>73.13932989739125</v>
+        <v>73.13932989739124</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>24280.08369458246</v>
@@ -30610,7 +30610,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>53063.31559107962</v>
+        <v>53063.3155910796</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>0</v>
@@ -30619,10 +30619,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="164" t="n">
-        <v>56.57719073989276</v>
+        <v>56.57719073989277</v>
       </c>
       <c r="T10" s="161" t="n">
-        <v>53119.89278181952</v>
+        <v>53119.8927818195</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" thickBot="1">
@@ -30983,16 +30983,16 @@
         <v>64043.47173804005</v>
       </c>
       <c r="Q25" s="177" t="n">
-        <v>0.6180745700455468</v>
+        <v>0.6180745700455469</v>
       </c>
       <c r="R25" s="176" t="n">
-        <v>1245.565925394592</v>
+        <v>1245.565925394593</v>
       </c>
       <c r="S25" s="178" t="n">
         <v>122033.8634974797</v>
       </c>
       <c r="T25" s="72" t="n">
-        <v>51.41716743555845</v>
+        <v>51.41716743555844</v>
       </c>
       <c r="U25" s="179" t="n">
         <v>0.01964068839399623</v>
@@ -31217,7 +31217,7 @@
         <v>5140.863302994366</v>
       </c>
       <c r="Q28" s="186" t="n">
-        <v>0.04961375124474806</v>
+        <v>0.04961375124474807</v>
       </c>
       <c r="R28" s="185" t="n">
         <v>1064.71973903936</v>
@@ -31437,7 +31437,7 @@
         <v>3119.69215431199</v>
       </c>
       <c r="Q31" s="186" t="n">
-        <v>0.03010771175613126</v>
+        <v>0.03010771175613127</v>
       </c>
       <c r="R31" s="185" t="n">
         <v>369.2095633028896</v>
@@ -31821,7 +31821,7 @@
         <v>904.0980860287003</v>
       </c>
       <c r="Q36" s="186" t="n">
-        <v>0.00872532391883557</v>
+        <v>0.008725323918835572</v>
       </c>
       <c r="R36" s="185" t="n">
         <v>393.9726767670575</v>
@@ -31974,13 +31974,13 @@
         </is>
       </c>
       <c r="P38" s="185" t="n">
-        <v>624.3542920536846</v>
+        <v>624.3542920536847</v>
       </c>
       <c r="Q38" s="186" t="n">
-        <v>0.006025555769300376</v>
+        <v>0.006025555769300379</v>
       </c>
       <c r="R38" s="185" t="n">
-        <v>320.5188229601124</v>
+        <v>320.5188229601125</v>
       </c>
       <c r="S38" s="187" t="n">
         <v>1484.009937210982</v>
@@ -31989,7 +31989,7 @@
         <v>1.947948910730224</v>
       </c>
       <c r="U38" s="197" t="n">
-        <v>0.0007440911172523674</v>
+        <v>0.0007440911172523673</v>
       </c>
       <c r="W38" s="184" t="n">
         <v>14</v>
@@ -32113,7 +32113,7 @@
         <v>477.9959493529775</v>
       </c>
       <c r="Q40" s="186" t="n">
-        <v>0.004613071916030639</v>
+        <v>0.00461307191603064</v>
       </c>
       <c r="R40" s="185" t="n">
         <v>144.4212983457928</v>
@@ -32193,7 +32193,7 @@
         <v>390.2886008527829</v>
       </c>
       <c r="Q41" s="186" t="n">
-        <v>0.003766620587847978</v>
+        <v>0.003766620587847979</v>
       </c>
       <c r="R41" s="185" t="n">
         <v>323.3293342057707</v>
@@ -32353,7 +32353,7 @@
         <v>78.44958836750484</v>
       </c>
       <c r="Q43" s="186" t="n">
-        <v>0.0007571059826179806</v>
+        <v>0.0007571059826179807</v>
       </c>
       <c r="R43" s="185" t="n">
         <v>18.96215467443058</v>
@@ -32433,7 +32433,7 @@
         <v>63.47729586781411</v>
       </c>
       <c r="Q44" s="207" t="n">
-        <v>0.000612610486071595</v>
+        <v>0.0006126104860715951</v>
       </c>
       <c r="R44" s="206" t="n">
         <v>1479.292057785772</v>
@@ -32681,10 +32681,10 @@
         </is>
       </c>
       <c r="Z49" s="72" t="n">
-        <v>2094.242396546215</v>
+        <v>2094.242396546214</v>
       </c>
       <c r="AA49" s="180" t="n">
-        <v>0.9311084917789626</v>
+        <v>0.9311084917789624</v>
       </c>
       <c r="AB49" s="181" t="n">
         <v>2340560.823126751</v>
@@ -32717,7 +32717,7 @@
         <v>3197.724823815559</v>
       </c>
       <c r="Q50" s="186" t="n">
-        <v>0.1263242016253596</v>
+        <v>0.1263242016253595</v>
       </c>
       <c r="R50" s="185" t="n">
         <v>527.0194963707871</v>
@@ -32877,7 +32877,7 @@
         <v>2406.838377559937</v>
       </c>
       <c r="Q52" s="186" t="n">
-        <v>0.09508070682697102</v>
+        <v>0.09508070682697101</v>
       </c>
       <c r="R52" s="185" t="n">
         <v>394.7212319771705</v>
@@ -33102,7 +33102,7 @@
         <v>860.2452755421123</v>
       </c>
       <c r="Q55" s="186" t="n">
-        <v>0.03398347375781348</v>
+        <v>0.03398347375781347</v>
       </c>
       <c r="R55" s="185" t="n">
         <v>434.2482549065662</v>
@@ -33252,7 +33252,7 @@
         <v>468.2168366195239</v>
       </c>
       <c r="Q57" s="186" t="n">
-        <v>0.01849662536094579</v>
+        <v>0.01849662536094578</v>
       </c>
       <c r="R57" s="185" t="n">
         <v>300.4550286460055</v>
@@ -33402,7 +33402,7 @@
         <v>89.82407690554986</v>
       </c>
       <c r="Q59" s="186" t="n">
-        <v>0.003548446294477952</v>
+        <v>0.003548446294477951</v>
       </c>
       <c r="R59" s="185" t="n">
         <v>183.292121809447</v>
@@ -35452,13 +35452,13 @@
         </is>
       </c>
       <c r="P97" s="176" t="n">
-        <v>41526.77769111137</v>
+        <v>41526.77769111138</v>
       </c>
       <c r="Q97" s="177" t="n">
-        <v>0.7817556760077661</v>
+        <v>0.7817556760077664</v>
       </c>
       <c r="R97" s="176" t="n">
-        <v>1610.338386144383</v>
+        <v>1610.338386144384</v>
       </c>
       <c r="S97" s="178" t="n">
         <v>79149.76354203306</v>
@@ -35530,7 +35530,7 @@
         <v>3855.647477245774</v>
       </c>
       <c r="Q98" s="186" t="n">
-        <v>0.07258387160309525</v>
+        <v>0.07258387160309528</v>
       </c>
       <c r="R98" s="185" t="n">
         <v>1064.71973903936</v>
@@ -35605,7 +35605,7 @@
         <v>3120.721621618522</v>
       </c>
       <c r="Q99" s="186" t="n">
-        <v>0.05874864308247627</v>
+        <v>0.05874864308247629</v>
       </c>
       <c r="R99" s="185" t="n">
         <v>935.0466305843712</v>
@@ -35680,7 +35680,7 @@
         <v>1267.7614891689</v>
       </c>
       <c r="Q100" s="186" t="n">
-        <v>0.02386604006103709</v>
+        <v>0.0238660400610371</v>
       </c>
       <c r="R100" s="185" t="n">
         <v>420.5533201933616</v>
@@ -35830,10 +35830,10 @@
         <v>1048.724529555171</v>
       </c>
       <c r="Q102" s="186" t="n">
-        <v>0.01974259499849934</v>
+        <v>0.01974259499849935</v>
       </c>
       <c r="R102" s="185" t="n">
-        <v>273.0718476443264</v>
+        <v>273.0718476443265</v>
       </c>
       <c r="S102" s="187" t="n">
         <v>1487.23923495937</v>
@@ -35906,7 +35906,7 @@
         <v>477.9959493529775</v>
       </c>
       <c r="Q103" s="186" t="n">
-        <v>0.008998435883827188</v>
+        <v>0.008998435883827189</v>
       </c>
       <c r="R103" s="185" t="n">
         <v>144.4212983457928</v>
@@ -35981,7 +35981,7 @@
         <v>390.2886008527829</v>
       </c>
       <c r="Q104" s="186" t="n">
-        <v>0.007347315297789168</v>
+        <v>0.00734731529778917</v>
       </c>
       <c r="R104" s="185" t="n">
         <v>323.3293342057707</v>
@@ -36056,7 +36056,7 @@
         <v>156.1374554341608</v>
       </c>
       <c r="Q105" s="186" t="n">
-        <v>0.002939340560709856</v>
+        <v>0.002939340560709857</v>
       </c>
       <c r="R105" s="185" t="n">
         <v>400.7740002165402</v>
@@ -36084,10 +36084,10 @@
         </is>
       </c>
       <c r="Z105" s="84" t="n">
-        <v>1.596965595652399</v>
+        <v>1.5969655956524</v>
       </c>
       <c r="AA105" s="189" t="n">
-        <v>0.008704061842336729</v>
+        <v>0.008704061842336731</v>
       </c>
       <c r="AB105" s="190" t="n">
         <v>2562.952940567171</v>
@@ -36131,7 +36131,7 @@
         <v>63.47729586781411</v>
       </c>
       <c r="Q106" s="186" t="n">
-        <v>0.001194981626347323</v>
+        <v>0.001194981626347324</v>
       </c>
       <c r="R106" s="185" t="n">
         <v>1479.292057785772</v>
@@ -37171,7 +37171,7 @@
         <v>58.12481008580384</v>
       </c>
       <c r="Q145" s="72" t="n">
-        <v>51.46007802615733</v>
+        <v>51.46007802615732</v>
       </c>
       <c r="R145" s="238" t="n">
         <v>138934.1084378113</v>
@@ -37192,10 +37192,10 @@
         <v>15342.71504250832</v>
       </c>
       <c r="P146" s="84" t="n">
-        <v>32.37441038664758</v>
+        <v>32.37441038664759</v>
       </c>
       <c r="Q146" s="84" t="n">
-        <v>19.80354890009995</v>
+        <v>19.80354890009996</v>
       </c>
       <c r="R146" s="240" t="n">
         <v>45699.84667021004</v>
@@ -37216,7 +37216,7 @@
         <v>6048.064903563136</v>
       </c>
       <c r="P147" s="84" t="n">
-        <v>9.374396464881979</v>
+        <v>9.374396464881981</v>
       </c>
       <c r="Q147" s="84" t="n">
         <v>9.146347533057741</v>
@@ -37628,7 +37628,7 @@
         <v>0</v>
       </c>
       <c r="R165" s="240" t="n">
-        <v>41332.45343357507</v>
+        <v>41332.45343357508</v>
       </c>
       <c r="T165" s="172" t="n"/>
       <c r="U165" s="172" t="n"/>
@@ -39499,7 +39499,7 @@
         <v>58.12481008580384</v>
       </c>
       <c r="Q299" s="72" t="n">
-        <v>51.46007802615733</v>
+        <v>51.46007802615732</v>
       </c>
       <c r="R299" s="238" t="n">
         <v>138934.1084378113</v>
@@ -39518,10 +39518,10 @@
         <v>15342.71504250832</v>
       </c>
       <c r="P300" s="84" t="n">
-        <v>32.37441038664758</v>
+        <v>32.37441038664759</v>
       </c>
       <c r="Q300" s="84" t="n">
-        <v>19.80354890009995</v>
+        <v>19.80354890009996</v>
       </c>
       <c r="R300" s="240" t="n">
         <v>45699.84667021004</v>
@@ -39540,7 +39540,7 @@
         <v>6048.064903563136</v>
       </c>
       <c r="P301" s="84" t="n">
-        <v>9.374396464881979</v>
+        <v>9.374396464881981</v>
       </c>
       <c r="Q301" s="84" t="n">
         <v>9.146347533057741</v>
@@ -39850,7 +39850,7 @@
         <v>0</v>
       </c>
       <c r="R316" s="240" t="n">
-        <v>41332.45343357507</v>
+        <v>41332.45343357508</v>
       </c>
     </row>
     <row r="317">
@@ -44057,7 +44057,7 @@
         </is>
       </c>
       <c r="AM654" s="84" t="n">
-        <v>0.3861512108415192</v>
+        <v>0.3861512108415193</v>
       </c>
       <c r="AN654" s="189" t="n">
         <v>0.0001475047339900249</v>
@@ -44745,7 +44745,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="164" t="n">
-        <v>55.2017180734054</v>
+        <v>55.20171807340541</v>
       </c>
       <c r="T10" s="161" t="n">
         <v>63290.39404055377</v>
@@ -45262,16 +45262,16 @@
         </is>
       </c>
       <c r="P27" s="185" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="Q27" s="186" t="n">
-        <v>0.05371672281917258</v>
+        <v>0.05371672281917257</v>
       </c>
       <c r="R27" s="185" t="n">
-        <v>686.0358204215186</v>
+        <v>686.0358204215185</v>
       </c>
       <c r="S27" s="187" t="n">
-        <v>8526.973997461851</v>
+        <v>8526.973997461853</v>
       </c>
       <c r="T27" s="84" t="n">
         <v>9.116896294001295</v>
@@ -45496,13 +45496,13 @@
         </is>
       </c>
       <c r="P30" s="185" t="n">
-        <v>3023.486740610278</v>
+        <v>3023.486740610279</v>
       </c>
       <c r="Q30" s="186" t="n">
-        <v>0.02596711913315185</v>
+        <v>0.02596711913315186</v>
       </c>
       <c r="R30" s="185" t="n">
-        <v>454.357487294121</v>
+        <v>454.3574872941211</v>
       </c>
       <c r="S30" s="187" t="n">
         <v>4220.676003974906</v>
@@ -47289,10 +47289,10 @@
         </is>
       </c>
       <c r="Z56" s="84" t="n">
-        <v>3.071199740915822</v>
+        <v>3.071199740915823</v>
       </c>
       <c r="AA56" s="189" t="n">
-        <v>0.001156995767214646</v>
+        <v>0.001156995767214647</v>
       </c>
       <c r="AB56" s="190" t="n">
         <v>2121.693393398342</v>
@@ -51178,7 +51178,7 @@
         <v>78879.6483755581</v>
       </c>
       <c r="P145" s="72" t="n">
-        <v>68.10200542396778</v>
+        <v>68.10200542396777</v>
       </c>
       <c r="Q145" s="72" t="n">
         <v>61.70386264670712</v>
@@ -51223,10 +51223,10 @@
         </is>
       </c>
       <c r="O147" s="239" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="P147" s="84" t="n">
-        <v>9.284039392724651</v>
+        <v>9.284039392724653</v>
       </c>
       <c r="Q147" s="84" t="n">
         <v>9.116896294001295</v>
@@ -51271,7 +51271,7 @@
         </is>
       </c>
       <c r="O149" s="239" t="n">
-        <v>3023.486740610278</v>
+        <v>3023.486740610279</v>
       </c>
       <c r="P149" s="84" t="n">
         <v>6.654422619106247</v>
@@ -51490,7 +51490,7 @@
         <v>0</v>
       </c>
       <c r="P158" s="84" t="n">
-        <v>2723.923475561104</v>
+        <v>2723.923475561105</v>
       </c>
       <c r="Q158" s="84" t="n">
         <v>0</v>
@@ -51927,7 +51927,7 @@
         <v>0</v>
       </c>
       <c r="P180" s="84" t="n">
-        <v>6.068929356646683</v>
+        <v>6.068929356646684</v>
       </c>
       <c r="Q180" s="84" t="n">
         <v>0</v>
@@ -53506,7 +53506,7 @@
         <v>78879.6483755581</v>
       </c>
       <c r="P299" s="72" t="n">
-        <v>68.10200542396778</v>
+        <v>68.10200542396777</v>
       </c>
       <c r="Q299" s="72" t="n">
         <v>61.70386264670712</v>
@@ -53547,10 +53547,10 @@
         </is>
       </c>
       <c r="O301" s="239" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="P301" s="84" t="n">
-        <v>9.284039392724651</v>
+        <v>9.284039392724653</v>
       </c>
       <c r="Q301" s="84" t="n">
         <v>9.116896294001295</v>
@@ -53591,7 +53591,7 @@
         </is>
       </c>
       <c r="O303" s="239" t="n">
-        <v>3023.486740610278</v>
+        <v>3023.486740610279</v>
       </c>
       <c r="P303" s="84" t="n">
         <v>6.654422619106247</v>
@@ -53770,7 +53770,7 @@
         <v>0</v>
       </c>
       <c r="P311" s="84" t="n">
-        <v>2723.923475561104</v>
+        <v>2723.923475561105</v>
       </c>
       <c r="Q311" s="84" t="n">
         <v>0</v>
@@ -54110,7 +54110,7 @@
         <v>0</v>
       </c>
       <c r="P330" s="84" t="n">
-        <v>6.068929356646683</v>
+        <v>6.068929356646684</v>
       </c>
       <c r="Q330" s="84" t="n">
         <v>0</v>
@@ -58756,7 +58756,7 @@
         </is>
       </c>
       <c r="P8" s="158" t="n">
-        <v>24558.16322472382</v>
+        <v>24558.16322472383</v>
       </c>
       <c r="Q8" s="159" t="n">
         <v>0</v>
@@ -58765,7 +58765,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="160" t="n">
-        <v>15.17293138172418</v>
+        <v>15.17293138172419</v>
       </c>
       <c r="T8" s="161" t="n">
         <v>24573.33615610555</v>
@@ -58778,7 +58778,7 @@
         </is>
       </c>
       <c r="P9" s="162" t="n">
-        <v>30649.49937406527</v>
+        <v>30649.49937406526</v>
       </c>
       <c r="Q9" s="163" t="n">
         <v>0</v>
@@ -58787,7 +58787,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>86.95554096977129</v>
+        <v>86.95554096977136</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>30736.45491503504</v>
@@ -58809,7 +58809,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="164" t="n">
-        <v>60.79748202894537</v>
+        <v>60.7974820289454</v>
       </c>
       <c r="T10" s="161" t="n">
         <v>69103.87927750955</v>
@@ -59170,13 +59170,13 @@
         </is>
       </c>
       <c r="P25" s="176" t="n">
-        <v>97701.03174199554</v>
+        <v>97701.03174199555</v>
       </c>
       <c r="Q25" s="177" t="n">
-        <v>0.778575823199579</v>
+        <v>0.7785758231995792</v>
       </c>
       <c r="R25" s="176" t="n">
-        <v>1322.000815884655</v>
+        <v>1322.000815884656</v>
       </c>
       <c r="S25" s="178" t="n">
         <v>178793.5289474547</v>
@@ -59326,16 +59326,16 @@
         </is>
       </c>
       <c r="P27" s="185" t="n">
-        <v>6531.668755170008</v>
+        <v>6531.668755170009</v>
       </c>
       <c r="Q27" s="186" t="n">
         <v>0.05205062103492162</v>
       </c>
       <c r="R27" s="185" t="n">
-        <v>718.7499406568776</v>
+        <v>718.7499406568777</v>
       </c>
       <c r="S27" s="187" t="n">
-        <v>8691.078714336749</v>
+        <v>8691.078714336747</v>
       </c>
       <c r="T27" s="84" t="n">
         <v>9.087539887934609</v>
@@ -60735,7 +60735,7 @@
         <v>17330.67268191621</v>
       </c>
       <c r="Q49" s="177" t="n">
-        <v>0.705263321667872</v>
+        <v>0.7052633216678719</v>
       </c>
       <c r="R49" s="176" t="n">
         <v>626.1098719798465</v>
@@ -60799,7 +60799,7 @@
         <v>2587.985663313055</v>
       </c>
       <c r="Q50" s="186" t="n">
-        <v>0.1053168217319991</v>
+        <v>0.105316821731999</v>
       </c>
       <c r="R50" s="185" t="n">
         <v>427.1759511200195</v>
@@ -60884,7 +60884,7 @@
         <v>2170.917801783211</v>
       </c>
       <c r="Q51" s="186" t="n">
-        <v>0.08834444733072271</v>
+        <v>0.08834444733072269</v>
       </c>
       <c r="R51" s="185" t="n">
         <v>1817.755657688419</v>
@@ -61034,7 +61034,7 @@
         <v>654.457389393505</v>
       </c>
       <c r="Q53" s="186" t="n">
-        <v>0.02663282613463525</v>
+        <v>0.02663282613463524</v>
       </c>
       <c r="R53" s="185" t="n">
         <v>269.2954945436377</v>
@@ -61184,7 +61184,7 @@
         <v>291.495932372991</v>
       </c>
       <c r="Q55" s="186" t="n">
-        <v>0.01186228563029548</v>
+        <v>0.01186228563029547</v>
       </c>
       <c r="R55" s="185" t="n">
         <v>309.6936684348626</v>
@@ -61287,10 +61287,10 @@
         </is>
       </c>
       <c r="Z56" s="84" t="n">
-        <v>3.073226732744828</v>
+        <v>3.073226732744827</v>
       </c>
       <c r="AA56" s="189" t="n">
-        <v>0.0009760196319657706</v>
+        <v>0.0009760196319657705</v>
       </c>
       <c r="AB56" s="190" t="n">
         <v>2204.541955074536</v>
@@ -62103,7 +62103,7 @@
         <v>17106.59643424521</v>
       </c>
       <c r="Q73" s="177" t="n">
-        <v>0.5565572373760431</v>
+        <v>0.5565572373760432</v>
       </c>
       <c r="R73" s="176" t="n">
         <v>1854.043827386841</v>
@@ -62178,7 +62178,7 @@
         <v>7879.044506212418</v>
       </c>
       <c r="Q74" s="186" t="n">
-        <v>0.2563420058686828</v>
+        <v>0.2563420058686829</v>
       </c>
       <c r="R74" s="185" t="n">
         <v>1491.224414808953</v>
@@ -62253,7 +62253,7 @@
         <v>3943.683091856954</v>
       </c>
       <c r="Q75" s="186" t="n">
-        <v>0.1283063743934848</v>
+        <v>0.1283063743934849</v>
       </c>
       <c r="R75" s="185" t="n">
         <v>1301.897919730594</v>
@@ -62328,7 +62328,7 @@
         <v>1744.893546917372</v>
       </c>
       <c r="Q76" s="186" t="n">
-        <v>0.05676951202540408</v>
+        <v>0.0567695120254041</v>
       </c>
       <c r="R76" s="185" t="n">
         <v>926.9125630228345</v>
@@ -62403,7 +62403,7 @@
         <v>62.23733580309131</v>
       </c>
       <c r="Q77" s="186" t="n">
-        <v>0.002024870336385062</v>
+        <v>0.002024870336385063</v>
       </c>
       <c r="R77" s="185" t="n">
         <v>184.1178980784285</v>
@@ -65131,7 +65131,7 @@
         </is>
       </c>
       <c r="O146" s="239" t="n">
-        <v>8594.980611133036</v>
+        <v>8594.980611133034</v>
       </c>
       <c r="P146" s="84" t="n">
         <v>16.2245420212208</v>
@@ -65155,7 +65155,7 @@
         </is>
       </c>
       <c r="O147" s="239" t="n">
-        <v>6531.668755170009</v>
+        <v>6531.668755170008</v>
       </c>
       <c r="P147" s="84" t="n">
         <v>9.254144785880076</v>
@@ -65374,7 +65374,7 @@
         <v>0</v>
       </c>
       <c r="P156" s="84" t="n">
-        <v>3268.708170673324</v>
+        <v>3268.708170673325</v>
       </c>
       <c r="Q156" s="84" t="n">
         <v>0</v>
@@ -67457,7 +67457,7 @@
         </is>
       </c>
       <c r="O300" s="239" t="n">
-        <v>8594.980611133036</v>
+        <v>8594.980611133034</v>
       </c>
       <c r="P300" s="84" t="n">
         <v>16.2245420212208</v>
@@ -67479,7 +67479,7 @@
         </is>
       </c>
       <c r="O301" s="239" t="n">
-        <v>6531.668755170009</v>
+        <v>6531.668755170008</v>
       </c>
       <c r="P301" s="84" t="n">
         <v>9.254144785880076</v>
@@ -67658,7 +67658,7 @@
         <v>0</v>
       </c>
       <c r="P309" s="84" t="n">
-        <v>3268.708170673324</v>
+        <v>3268.708170673325</v>
       </c>
       <c r="Q309" s="84" t="n">
         <v>0</v>
@@ -70871,10 +70871,10 @@
         </is>
       </c>
       <c r="AM607" s="72" t="n">
-        <v>3261.22491731152</v>
+        <v>3261.224917311521</v>
       </c>
       <c r="AN607" s="180" t="n">
-        <v>0.9084179469991258</v>
+        <v>0.9084179469991259</v>
       </c>
       <c r="AO607" s="181" t="n">
         <v>4068652.182517468</v>
